--- a/MiraVos/Product_Cost_r0_1.xlsx
+++ b/MiraVos/Product_Cost_r0_1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gz173f\Desktop\Git\dailyworkspace\Personal\EMBA\MiraVos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gz173f\Desktop\Git\brian-stuff\MiraVos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D237A06-E09E-4F97-B128-6E744DE39B83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2151979F-9824-4F2C-A9E8-9939DCB8D3E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3408" yWindow="2340" windowWidth="17256" windowHeight="8868" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Product Cost rev1 Stick Form" sheetId="1" r:id="rId1"/>
@@ -165,12 +165,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="12">
@@ -302,17 +308,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
@@ -326,6 +323,24 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -398,7 +413,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>138176</xdr:colOff>
+      <xdr:colOff>134366</xdr:colOff>
       <xdr:row>99</xdr:row>
       <xdr:rowOff>152968</xdr:rowOff>
     </xdr:to>
@@ -702,1774 +717,1774 @@
   <dimension ref="A1:AC31"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.77734375" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.33203125" style="4" customWidth="1"/>
-    <col min="5" max="5" width="12" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.44140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="8.88671875" style="4"/>
-    <col min="11" max="11" width="15.77734375" style="4" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12" style="4" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="12.33203125" style="4" customWidth="1"/>
-    <col min="15" max="15" width="12" style="4" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.44140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12" style="4" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="20.109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="8.88671875" style="4"/>
-    <col min="21" max="21" width="15.77734375" style="4" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12" style="4" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.33203125" style="4" customWidth="1"/>
-    <col min="25" max="25" width="12" style="4" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.44140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="12" style="4" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="20.109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="8.88671875" style="4"/>
+    <col min="1" max="1" width="15.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="8.88671875" style="1"/>
+    <col min="11" max="11" width="15.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="12.33203125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="20.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="8.88671875" style="1"/>
+    <col min="21" max="21" width="15.77734375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="12.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="12.33203125" style="1" customWidth="1"/>
+    <col min="25" max="25" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="20.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="3"/>
-      <c r="K1" s="1" t="s">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="I1" s="16"/>
+      <c r="K1" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="3"/>
-      <c r="U1" s="1" t="s">
+      <c r="L1" s="15"/>
+      <c r="M1" s="15"/>
+      <c r="N1" s="15"/>
+      <c r="O1" s="15"/>
+      <c r="P1" s="15"/>
+      <c r="Q1" s="15"/>
+      <c r="R1" s="15"/>
+      <c r="S1" s="16"/>
+      <c r="U1" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="V1" s="2"/>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2"/>
-      <c r="Y1" s="2"/>
-      <c r="Z1" s="2"/>
-      <c r="AA1" s="2"/>
-      <c r="AB1" s="2"/>
-      <c r="AC1" s="3"/>
+      <c r="V1" s="18"/>
+      <c r="W1" s="18"/>
+      <c r="X1" s="18"/>
+      <c r="Y1" s="18"/>
+      <c r="Z1" s="18"/>
+      <c r="AA1" s="18"/>
+      <c r="AB1" s="18"/>
+      <c r="AC1" s="19"/>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="7"/>
-      <c r="K2" s="5" t="s">
+      <c r="I2" s="4"/>
+      <c r="K2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="L2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="M2" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="N2" s="15" t="s">
+      <c r="N2" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="O2" s="6" t="s">
+      <c r="O2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="P2" s="6" t="s">
+      <c r="P2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="Q2" s="6" t="s">
+      <c r="Q2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="R2" s="6" t="s">
+      <c r="R2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S2" s="7"/>
-      <c r="U2" s="5" t="s">
+      <c r="S2" s="4"/>
+      <c r="U2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="V2" s="6" t="s">
+      <c r="V2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W2" s="6" t="s">
+      <c r="W2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="X2" s="15" t="s">
+      <c r="X2" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="Y2" s="6" t="s">
+      <c r="Y2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="Z2" s="6" t="s">
+      <c r="Z2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="AA2" s="6" t="s">
+      <c r="AA2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="AB2" s="6" t="s">
+      <c r="AB2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC2" s="7"/>
+      <c r="AC2" s="4"/>
     </row>
     <row r="3" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="3">
         <v>250</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="3">
         <f>E3/F3/1000</f>
         <v>4.7969999999999996E-5</v>
       </c>
-      <c r="D3" s="6">
+      <c r="D3" s="3">
         <f>B3*C3</f>
         <v>1.19925E-2</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="3">
         <v>47.97</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="3">
         <v>1000</v>
       </c>
-      <c r="G3" s="6">
+      <c r="G3" s="3">
         <f>(F3*1000)/B3</f>
         <v>4000</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="7"/>
-      <c r="K3" s="5" t="s">
+      <c r="I3" s="4"/>
+      <c r="K3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="L3" s="6">
+      <c r="L3" s="3">
         <v>250</v>
       </c>
-      <c r="M3" s="6">
+      <c r="M3" s="3">
         <f>(O3/P3)/1000</f>
         <v>4.7969999999999996E-5</v>
       </c>
-      <c r="N3" s="6">
+      <c r="N3" s="3">
         <f>L3*M3</f>
         <v>1.19925E-2</v>
       </c>
-      <c r="O3" s="6">
+      <c r="O3" s="3">
         <v>47.97</v>
       </c>
-      <c r="P3" s="6">
+      <c r="P3" s="3">
         <v>1000</v>
       </c>
-      <c r="Q3" s="6">
+      <c r="Q3" s="3">
         <f>(P3*1000)/L3</f>
         <v>4000</v>
       </c>
-      <c r="R3" s="6" t="s">
+      <c r="R3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="S3" s="7"/>
-      <c r="U3" s="5"/>
-      <c r="V3" s="6"/>
-      <c r="W3" s="6"/>
-      <c r="X3" s="6">
+      <c r="S3" s="4"/>
+      <c r="U3" s="2"/>
+      <c r="V3" s="3"/>
+      <c r="W3" s="3"/>
+      <c r="X3" s="3">
         <f>V3*W3</f>
         <v>0</v>
       </c>
-      <c r="Y3" s="6"/>
-      <c r="Z3" s="6"/>
-      <c r="AA3" s="6"/>
-      <c r="AB3" s="6"/>
-      <c r="AC3" s="7"/>
+      <c r="Y3" s="3"/>
+      <c r="Z3" s="3"/>
+      <c r="AA3" s="3"/>
+      <c r="AB3" s="3"/>
+      <c r="AC3" s="4"/>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="3">
         <v>5000</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="3">
         <f>E4/F4/1000</f>
         <v>2.8969999999999999E-5</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="3">
         <f t="shared" ref="D4:D10" si="0">B4*C4</f>
         <v>0.14485000000000001</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="3">
         <v>28.97</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="3">
         <v>1000</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="3">
         <f>(F4*1000)/B4</f>
         <v>200</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="I4" s="7"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6">
+      <c r="I4" s="4"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3">
         <f>L4*M4</f>
         <v>0</v>
       </c>
-      <c r="O4" s="6"/>
-      <c r="P4" s="6"/>
-      <c r="Q4" s="6"/>
-      <c r="R4" s="6"/>
-      <c r="S4" s="7"/>
-      <c r="U4" s="5"/>
-      <c r="V4" s="6"/>
-      <c r="W4" s="6"/>
-      <c r="X4" s="6">
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3"/>
+      <c r="R4" s="3"/>
+      <c r="S4" s="4"/>
+      <c r="U4" s="2"/>
+      <c r="V4" s="3"/>
+      <c r="W4" s="3"/>
+      <c r="X4" s="3">
         <f t="shared" ref="X4:X10" si="1">V4*W4</f>
         <v>0</v>
       </c>
-      <c r="Y4" s="6"/>
-      <c r="Z4" s="6"/>
-      <c r="AA4" s="6"/>
-      <c r="AB4" s="6"/>
-      <c r="AC4" s="7"/>
+      <c r="Y4" s="3"/>
+      <c r="Z4" s="3"/>
+      <c r="AA4" s="3"/>
+      <c r="AB4" s="3"/>
+      <c r="AC4" s="4"/>
     </row>
     <row r="5" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="3">
         <v>500</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="3">
         <f>E5/F5/1000</f>
         <v>8.5997794928335176E-5</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="3">
         <f t="shared" si="0"/>
         <v>4.2998897464167588E-2</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="3">
         <v>156</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="3">
         <v>1814</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="3">
         <f>(F5*1000)/B5</f>
         <v>3628</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I5" s="7"/>
-      <c r="K5" s="5" t="s">
+      <c r="I5" s="4"/>
+      <c r="K5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="L5" s="6">
+      <c r="L5" s="3">
         <v>500</v>
       </c>
-      <c r="M5" s="6">
+      <c r="M5" s="3">
         <f>(O5/P5)/1000</f>
         <v>8.5997794928335176E-5</v>
       </c>
-      <c r="N5" s="6">
+      <c r="N5" s="3">
         <f>M5*L5</f>
         <v>4.2998897464167588E-2</v>
       </c>
-      <c r="O5" s="6">
+      <c r="O5" s="3">
         <v>156</v>
       </c>
-      <c r="P5" s="6">
+      <c r="P5" s="3">
         <v>1814</v>
       </c>
-      <c r="Q5" s="6">
+      <c r="Q5" s="3">
         <f>(P5*1000)/L5</f>
         <v>3628</v>
       </c>
-      <c r="R5" s="6" t="s">
+      <c r="R5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="S5" s="7"/>
-      <c r="U5" s="5" t="s">
+      <c r="S5" s="4"/>
+      <c r="U5" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="V5" s="6">
+      <c r="V5" s="3">
         <v>500</v>
       </c>
-      <c r="W5" s="6">
+      <c r="W5" s="3">
         <f>Y5/Z5/1000</f>
         <v>8.5997794928335176E-5</v>
       </c>
-      <c r="X5" s="6">
+      <c r="X5" s="3">
         <f t="shared" si="1"/>
         <v>4.2998897464167588E-2</v>
       </c>
-      <c r="Y5" s="6">
+      <c r="Y5" s="3">
         <v>156</v>
       </c>
-      <c r="Z5" s="6">
+      <c r="Z5" s="3">
         <v>1814</v>
       </c>
-      <c r="AA5" s="6">
+      <c r="AA5" s="3">
         <f>(Z5*1000)/V5</f>
         <v>3628</v>
       </c>
-      <c r="AB5" s="6" t="s">
+      <c r="AB5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AC5" s="7"/>
+      <c r="AC5" s="4"/>
     </row>
     <row r="6" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="3">
         <v>6000</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="3">
         <f>E6/F6/1000</f>
         <v>3.1970000000000001E-5</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="3">
         <f t="shared" si="0"/>
         <v>0.19181999999999999</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="3">
         <v>31.97</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="3">
         <v>1000</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="3">
         <f>(F6*1000)/B6</f>
         <v>166.66666666666666</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="H6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="I6" s="7"/>
-      <c r="K6" s="5" t="s">
+      <c r="I6" s="4"/>
+      <c r="K6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="L6" s="6">
+      <c r="L6" s="3">
         <v>6000</v>
       </c>
-      <c r="M6" s="6">
+      <c r="M6" s="3">
         <f>O6/P6/1000</f>
         <v>3.1970000000000001E-5</v>
       </c>
-      <c r="N6" s="6">
+      <c r="N6" s="3">
         <f>M6*L6</f>
         <v>0.19181999999999999</v>
       </c>
-      <c r="O6" s="6">
+      <c r="O6" s="3">
         <v>31.97</v>
       </c>
-      <c r="P6" s="6">
+      <c r="P6" s="3">
         <v>1000</v>
       </c>
-      <c r="Q6" s="6">
+      <c r="Q6" s="3">
         <f>(P6*1000)/L6</f>
         <v>166.66666666666666</v>
       </c>
-      <c r="R6" s="6" t="s">
+      <c r="R6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="S6" s="7"/>
-      <c r="U6" s="5" t="s">
+      <c r="S6" s="4"/>
+      <c r="U6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="V6" s="6">
+      <c r="V6" s="3">
         <v>6000</v>
       </c>
-      <c r="W6" s="6">
+      <c r="W6" s="3">
         <f>Y6/Z6/1000</f>
         <v>3.1970000000000001E-5</v>
       </c>
-      <c r="X6" s="6">
+      <c r="X6" s="3">
         <f t="shared" si="1"/>
         <v>0.19181999999999999</v>
       </c>
-      <c r="Y6" s="6">
+      <c r="Y6" s="3">
         <v>31.97</v>
       </c>
-      <c r="Z6" s="6">
+      <c r="Z6" s="3">
         <v>1000</v>
       </c>
-      <c r="AA6" s="6">
+      <c r="AA6" s="3">
         <f>(Z6*1000)/V6</f>
         <v>166.66666666666666</v>
       </c>
-      <c r="AB6" s="6" t="s">
+      <c r="AB6" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AC6" s="7"/>
+      <c r="AC6" s="4"/>
     </row>
     <row r="7" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="3">
         <v>1800</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C7" s="3">
         <f>E7/F7/1000</f>
         <v>2.6969999999999998E-5</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="3">
         <f t="shared" si="0"/>
         <v>4.8545999999999999E-2</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="3">
         <v>26.97</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="3">
         <v>1000</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="3">
         <f>(F7*1000)/B7</f>
         <v>555.55555555555554</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="H7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="I7" s="7"/>
-      <c r="K7" s="5" t="s">
+      <c r="I7" s="4"/>
+      <c r="K7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="L7" s="6">
+      <c r="L7" s="3">
         <v>1800</v>
       </c>
-      <c r="M7" s="6">
+      <c r="M7" s="3">
         <f>O7/P7/1000</f>
         <v>2.6969999999999998E-5</v>
       </c>
-      <c r="N7" s="6">
+      <c r="N7" s="3">
         <f>M7*L7</f>
         <v>4.8545999999999999E-2</v>
       </c>
-      <c r="O7" s="6">
+      <c r="O7" s="3">
         <v>26.97</v>
       </c>
-      <c r="P7" s="6">
+      <c r="P7" s="3">
         <v>1000</v>
       </c>
-      <c r="Q7" s="6">
+      <c r="Q7" s="3">
         <f>(P7*1000)/L7</f>
         <v>555.55555555555554</v>
       </c>
-      <c r="R7" s="6" t="s">
+      <c r="R7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="S7" s="7"/>
-      <c r="U7" s="5" t="s">
+      <c r="S7" s="4"/>
+      <c r="U7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="V7" s="6">
+      <c r="V7" s="3">
         <v>1800</v>
       </c>
-      <c r="W7" s="6">
+      <c r="W7" s="3">
         <f>Y7/Z7/1000</f>
         <v>2.6969999999999998E-5</v>
       </c>
-      <c r="X7" s="6">
+      <c r="X7" s="3">
         <f t="shared" si="1"/>
         <v>4.8545999999999999E-2</v>
       </c>
-      <c r="Y7" s="6">
+      <c r="Y7" s="3">
         <v>26.97</v>
       </c>
-      <c r="Z7" s="6">
+      <c r="Z7" s="3">
         <v>1000</v>
       </c>
-      <c r="AA7" s="6">
+      <c r="AA7" s="3">
         <f>(Z7*1000)/V7</f>
         <v>555.55555555555554</v>
       </c>
-      <c r="AB7" s="6" t="s">
+      <c r="AB7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AC7" s="7"/>
+      <c r="AC7" s="4"/>
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6">
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="7"/>
-      <c r="K8" s="5" t="s">
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
+      <c r="I8" s="4"/>
+      <c r="K8" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6">
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3">
         <f t="shared" ref="N8:N10" si="2">L8*M8</f>
         <v>0</v>
       </c>
-      <c r="O8" s="6"/>
-      <c r="P8" s="6"/>
-      <c r="Q8" s="6"/>
-      <c r="R8" s="6"/>
-      <c r="S8" s="7"/>
-      <c r="U8" s="5" t="s">
+      <c r="O8" s="3"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="3"/>
+      <c r="R8" s="3"/>
+      <c r="S8" s="4"/>
+      <c r="U8" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="V8" s="6"/>
-      <c r="W8" s="6"/>
-      <c r="X8" s="6">
+      <c r="V8" s="3"/>
+      <c r="W8" s="3"/>
+      <c r="X8" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Y8" s="6"/>
-      <c r="Z8" s="6"/>
-      <c r="AA8" s="6"/>
-      <c r="AB8" s="6"/>
-      <c r="AC8" s="7"/>
+      <c r="Y8" s="3"/>
+      <c r="Z8" s="3"/>
+      <c r="AA8" s="3"/>
+      <c r="AB8" s="3"/>
+      <c r="AC8" s="4"/>
     </row>
     <row r="9" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6">
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="7"/>
-      <c r="K9" s="5" t="s">
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
+      <c r="I9" s="4"/>
+      <c r="K9" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6">
+      <c r="L9" s="3"/>
+      <c r="M9" s="3"/>
+      <c r="N9" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O9" s="6"/>
-      <c r="P9" s="6"/>
-      <c r="Q9" s="6"/>
-      <c r="R9" s="6"/>
-      <c r="S9" s="7"/>
-      <c r="U9" s="5" t="s">
+      <c r="O9" s="3"/>
+      <c r="P9" s="3"/>
+      <c r="Q9" s="3"/>
+      <c r="R9" s="3"/>
+      <c r="S9" s="4"/>
+      <c r="U9" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="V9" s="6"/>
-      <c r="W9" s="6"/>
-      <c r="X9" s="6">
+      <c r="V9" s="3"/>
+      <c r="W9" s="3"/>
+      <c r="X9" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Y9" s="6"/>
-      <c r="Z9" s="6"/>
-      <c r="AA9" s="6"/>
-      <c r="AB9" s="6"/>
-      <c r="AC9" s="7"/>
+      <c r="Y9" s="3"/>
+      <c r="Z9" s="3"/>
+      <c r="AA9" s="3"/>
+      <c r="AB9" s="3"/>
+      <c r="AC9" s="4"/>
     </row>
     <row r="10" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6">
+      <c r="B10" s="3"/>
+      <c r="C10" s="3"/>
+      <c r="D10" s="3">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="7"/>
-      <c r="K10" s="5" t="s">
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
+      <c r="I10" s="4"/>
+      <c r="K10" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6">
+      <c r="L10" s="3"/>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O10" s="6"/>
-      <c r="P10" s="6"/>
-      <c r="Q10" s="6"/>
-      <c r="R10" s="6"/>
-      <c r="S10" s="7"/>
-      <c r="U10" s="5" t="s">
+      <c r="O10" s="3"/>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3"/>
+      <c r="R10" s="3"/>
+      <c r="S10" s="4"/>
+      <c r="U10" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="V10" s="6"/>
-      <c r="W10" s="6"/>
-      <c r="X10" s="6">
+      <c r="V10" s="3"/>
+      <c r="W10" s="3"/>
+      <c r="X10" s="3">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="Y10" s="6"/>
-      <c r="Z10" s="6"/>
-      <c r="AA10" s="6"/>
-      <c r="AB10" s="6"/>
-      <c r="AC10" s="7"/>
+      <c r="Y10" s="3"/>
+      <c r="Z10" s="3"/>
+      <c r="AA10" s="3"/>
+      <c r="AB10" s="3"/>
+      <c r="AC10" s="4"/>
     </row>
     <row r="11" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="14">
+      <c r="B11" s="11">
         <v>0.4</v>
       </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="G11" s="6">
+      <c r="C11" s="3"/>
+      <c r="D11" s="3"/>
+      <c r="E11" s="3"/>
+      <c r="G11" s="3">
         <f>MIN(G3:G7)</f>
         <v>166.66666666666666</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="H11" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I11" s="7"/>
-      <c r="K11" s="5" t="s">
+      <c r="I11" s="4"/>
+      <c r="K11" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="L11" s="14">
+      <c r="L11" s="11">
         <v>0.4</v>
       </c>
-      <c r="M11" s="6"/>
-      <c r="N11" s="6"/>
-      <c r="O11" s="6"/>
-      <c r="Q11" s="6">
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3"/>
+      <c r="Q11" s="3">
         <f>MIN(Q3:Q7)</f>
         <v>166.66666666666666</v>
       </c>
-      <c r="R11" s="6" t="s">
+      <c r="R11" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S11" s="7"/>
-      <c r="U11" s="5" t="s">
+      <c r="S11" s="4"/>
+      <c r="U11" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="V11" s="14">
+      <c r="V11" s="11">
         <v>0.4</v>
       </c>
-      <c r="W11" s="6"/>
-      <c r="X11" s="6"/>
-      <c r="Y11" s="6"/>
-      <c r="Z11" s="6" t="s">
+      <c r="W11" s="3"/>
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+      <c r="Z11" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AA11" s="6">
+      <c r="AA11" s="3">
         <f>MIN(AA3:AA7)</f>
         <v>166.66666666666666</v>
       </c>
-      <c r="AB11" s="6"/>
-      <c r="AC11" s="7"/>
+      <c r="AB11" s="3"/>
+      <c r="AC11" s="4"/>
     </row>
     <row r="12" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A12" s="8" t="s">
+      <c r="A12" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="9">
+      <c r="B12" s="6">
         <f>SUM(B3:B7)/1000</f>
         <v>13.55</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="6">
         <f>SUM(C3:C7)</f>
         <v>2.2187779492833517E-4</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D12" s="6">
         <f>SUM(D3:D10)</f>
         <v>0.44020739746416754</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="E12" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F12" s="10"/>
-      <c r="G12" s="6">
+      <c r="F12" s="7"/>
+      <c r="G12" s="3">
         <f>G11/B13</f>
         <v>16.666666666666664</v>
       </c>
-      <c r="H12" s="6" t="s">
+      <c r="H12" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="I12" s="7"/>
-      <c r="K12" s="8" t="s">
+      <c r="I12" s="4"/>
+      <c r="K12" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L12" s="9">
+      <c r="L12" s="6">
         <f>SUM(L3:L7)/1000</f>
         <v>8.5500000000000007</v>
       </c>
-      <c r="M12" s="9">
+      <c r="M12" s="6">
         <f>SUM(M3:M7)</f>
         <v>1.9290779492833518E-4</v>
       </c>
-      <c r="N12" s="9">
+      <c r="N12" s="6">
         <f>SUM(N3:N10)</f>
         <v>0.29535739746416756</v>
       </c>
-      <c r="O12" s="6" t="s">
+      <c r="O12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="Q12" s="6">
+      <c r="Q12" s="3">
         <f>Q11/L13</f>
         <v>16.666666666666664</v>
       </c>
-      <c r="R12" s="6" t="s">
+      <c r="R12" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="S12" s="7"/>
-      <c r="U12" s="8" t="s">
+      <c r="S12" s="4"/>
+      <c r="U12" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="V12" s="9">
+      <c r="V12" s="6">
         <f>SUM(V3:V7)/1000</f>
         <v>8.3000000000000007</v>
       </c>
-      <c r="W12" s="9">
+      <c r="W12" s="6">
         <f>SUM(W3:W7)</f>
         <v>1.4493779492833516E-4</v>
       </c>
-      <c r="X12" s="9">
+      <c r="X12" s="6">
         <f>SUM(X3:X10)</f>
         <v>0.28336489746416754</v>
       </c>
-      <c r="Y12" s="6" t="s">
+      <c r="Y12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="Z12" s="10" t="s">
+      <c r="Z12" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="AA12" s="4">
+      <c r="AA12" s="1">
         <f>AA11/V13</f>
         <v>16.666666666666664</v>
       </c>
-      <c r="AB12" s="6"/>
-      <c r="AC12" s="7"/>
+      <c r="AB12" s="3"/>
+      <c r="AC12" s="4"/>
     </row>
     <row r="13" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="12">
+      <c r="B13" s="9">
         <v>10</v>
       </c>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12">
+      <c r="C13" s="9"/>
+      <c r="D13" s="9">
         <f>D12*B13</f>
         <v>4.4020739746416755</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="13"/>
-      <c r="K13" s="11" t="s">
+      <c r="F13" s="9"/>
+      <c r="G13" s="9"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="10"/>
+      <c r="K13" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="L13" s="12">
+      <c r="L13" s="9">
         <v>10</v>
       </c>
-      <c r="M13" s="12"/>
-      <c r="N13" s="12">
+      <c r="M13" s="9"/>
+      <c r="N13" s="9">
         <f>N12*L13</f>
         <v>2.9535739746416754</v>
       </c>
-      <c r="O13" s="12" t="s">
+      <c r="O13" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="P13" s="12"/>
-      <c r="Q13" s="12"/>
-      <c r="R13" s="12"/>
-      <c r="S13" s="13"/>
-      <c r="U13" s="11" t="s">
+      <c r="P13" s="9"/>
+      <c r="Q13" s="9"/>
+      <c r="R13" s="9"/>
+      <c r="S13" s="10"/>
+      <c r="U13" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="V13" s="12">
+      <c r="V13" s="9">
         <v>10</v>
       </c>
-      <c r="W13" s="12"/>
-      <c r="X13" s="12">
+      <c r="W13" s="9"/>
+      <c r="X13" s="9">
         <f>X12*V13</f>
         <v>2.8336489746416755</v>
       </c>
-      <c r="Y13" s="12" t="s">
+      <c r="Y13" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="Z13" s="12"/>
-      <c r="AB13" s="12"/>
-      <c r="AC13" s="13"/>
+      <c r="Z13" s="9"/>
+      <c r="AB13" s="9"/>
+      <c r="AC13" s="10"/>
     </row>
     <row r="15" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="3"/>
-      <c r="K15" s="1" t="s">
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="16"/>
+      <c r="K15" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
-      <c r="P15" s="2"/>
-      <c r="Q15" s="2"/>
-      <c r="R15" s="2"/>
-      <c r="S15" s="3"/>
-      <c r="U15" s="1" t="s">
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="15"/>
+      <c r="O15" s="15"/>
+      <c r="P15" s="15"/>
+      <c r="Q15" s="15"/>
+      <c r="R15" s="15"/>
+      <c r="S15" s="16"/>
+      <c r="U15" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="V15" s="2"/>
-      <c r="W15" s="2"/>
-      <c r="X15" s="2"/>
-      <c r="Y15" s="2"/>
-      <c r="Z15" s="2"/>
-      <c r="AA15" s="2"/>
-      <c r="AB15" s="2"/>
-      <c r="AC15" s="3"/>
+      <c r="V15" s="15"/>
+      <c r="W15" s="15"/>
+      <c r="X15" s="15"/>
+      <c r="Y15" s="15"/>
+      <c r="Z15" s="15"/>
+      <c r="AA15" s="15"/>
+      <c r="AB15" s="15"/>
+      <c r="AC15" s="16"/>
     </row>
     <row r="16" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="D16" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F16" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G16" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H16" s="6" t="s">
+      <c r="H16" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="I16" s="7"/>
-      <c r="K16" s="5" t="s">
+      <c r="I16" s="4"/>
+      <c r="K16" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="L16" s="6" t="s">
+      <c r="L16" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M16" s="6" t="s">
+      <c r="M16" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="N16" s="15" t="s">
+      <c r="N16" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="O16" s="6" t="s">
+      <c r="O16" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="P16" s="6" t="s">
+      <c r="P16" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="Q16" s="6" t="s">
+      <c r="Q16" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="R16" s="6" t="s">
+      <c r="R16" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="S16" s="7"/>
-      <c r="U16" s="5" t="s">
+      <c r="S16" s="4"/>
+      <c r="U16" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="V16" s="6" t="s">
+      <c r="V16" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="W16" s="6" t="s">
+      <c r="W16" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="X16" s="15" t="s">
+      <c r="X16" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="Y16" s="6" t="s">
+      <c r="Y16" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="Z16" s="6" t="s">
+      <c r="Z16" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="AA16" s="6" t="s">
+      <c r="AA16" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="AB16" s="6" t="s">
+      <c r="AB16" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="AC16" s="7"/>
+      <c r="AC16" s="4"/>
     </row>
     <row r="17" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B17" s="6">
+      <c r="B17" s="3">
         <v>250</v>
       </c>
-      <c r="C17" s="6">
+      <c r="C17" s="3">
         <f>E17/F17/1000</f>
         <v>4.4700799999999997E-5</v>
       </c>
-      <c r="D17" s="6">
+      <c r="D17" s="3">
         <f t="shared" ref="D17:D24" si="3">B17*C17</f>
         <v>1.11752E-2</v>
       </c>
-      <c r="E17" s="6">
+      <c r="E17" s="3">
         <v>1117.52</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F17" s="3">
         <v>25000</v>
       </c>
-      <c r="G17" s="6">
+      <c r="G17" s="3">
         <f>(F17*1000)/B17</f>
         <v>100000</v>
       </c>
-      <c r="H17" s="6" t="s">
+      <c r="H17" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="I17" s="7"/>
-      <c r="K17" s="5" t="s">
+      <c r="I17" s="4"/>
+      <c r="K17" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="L17" s="6">
+      <c r="L17" s="3">
         <v>250</v>
       </c>
-      <c r="M17" s="6">
+      <c r="M17" s="3">
         <f>O17/P17/1000</f>
         <v>4.4700799999999997E-5</v>
       </c>
-      <c r="N17" s="6">
+      <c r="N17" s="3">
         <f t="shared" ref="N17:N24" si="4">L17*M17</f>
         <v>1.11752E-2</v>
       </c>
-      <c r="O17" s="6">
+      <c r="O17" s="3">
         <v>1117.52</v>
       </c>
-      <c r="P17" s="6">
+      <c r="P17" s="3">
         <v>25000</v>
       </c>
-      <c r="Q17" s="6">
+      <c r="Q17" s="3">
         <f>(P17*1000)/L17</f>
         <v>100000</v>
       </c>
-      <c r="R17" s="6" t="s">
+      <c r="R17" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="S17" s="7"/>
-      <c r="U17" s="5"/>
-      <c r="V17" s="6"/>
-      <c r="W17" s="6"/>
-      <c r="X17" s="6"/>
-      <c r="Y17" s="6"/>
-      <c r="Z17" s="6"/>
-      <c r="AA17" s="6"/>
-      <c r="AB17" s="6"/>
-      <c r="AC17" s="7"/>
+      <c r="S17" s="4"/>
+      <c r="U17" s="2"/>
+      <c r="V17" s="3"/>
+      <c r="W17" s="3"/>
+      <c r="X17" s="3"/>
+      <c r="Y17" s="3"/>
+      <c r="Z17" s="3"/>
+      <c r="AA17" s="3"/>
+      <c r="AB17" s="3"/>
+      <c r="AC17" s="4"/>
     </row>
     <row r="18" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B18" s="6">
+      <c r="B18" s="3">
         <v>5000</v>
       </c>
-      <c r="C18" s="6">
+      <c r="C18" s="3">
         <f>E18/F18/1000</f>
         <v>1.41444E-5</v>
       </c>
-      <c r="D18" s="6">
+      <c r="D18" s="3">
         <f t="shared" si="3"/>
         <v>7.0721999999999993E-2</v>
       </c>
-      <c r="E18" s="6">
+      <c r="E18" s="3">
         <v>353.61</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F18" s="3">
         <v>25000</v>
       </c>
-      <c r="G18" s="6">
+      <c r="G18" s="3">
         <f>(F18*1000)/B18</f>
         <v>5000</v>
       </c>
-      <c r="H18" s="6" t="s">
+      <c r="H18" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="I18" s="7"/>
-      <c r="K18" s="5"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="6">
+      <c r="I18" s="4"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O18" s="6"/>
-      <c r="P18" s="6"/>
-      <c r="Q18" s="6"/>
-      <c r="R18" s="6"/>
-      <c r="S18" s="7"/>
-      <c r="U18" s="5"/>
-      <c r="V18" s="6"/>
-      <c r="W18" s="6"/>
-      <c r="X18" s="6"/>
-      <c r="Y18" s="6"/>
-      <c r="Z18" s="6"/>
-      <c r="AA18" s="6"/>
-      <c r="AB18" s="6"/>
-      <c r="AC18" s="7"/>
+      <c r="O18" s="3"/>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="3"/>
+      <c r="R18" s="3"/>
+      <c r="S18" s="4"/>
+      <c r="U18" s="2"/>
+      <c r="V18" s="3"/>
+      <c r="W18" s="3"/>
+      <c r="X18" s="3"/>
+      <c r="Y18" s="3"/>
+      <c r="Z18" s="3"/>
+      <c r="AA18" s="3"/>
+      <c r="AB18" s="3"/>
+      <c r="AC18" s="4"/>
     </row>
     <row r="19" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B19" s="6">
+      <c r="B19" s="3">
         <v>500</v>
       </c>
-      <c r="C19" s="6">
+      <c r="C19" s="3">
         <f>E19/F19/1000</f>
         <v>7.7161653664426977E-5</v>
       </c>
-      <c r="D19" s="6">
+      <c r="D19" s="3">
         <f t="shared" si="3"/>
         <v>3.8580826832213491E-2</v>
       </c>
-      <c r="E19" s="6">
+      <c r="E19" s="3">
         <v>1540</v>
       </c>
-      <c r="F19" s="6">
+      <c r="F19" s="3">
         <v>19958.099999999999</v>
       </c>
-      <c r="G19" s="6">
+      <c r="G19" s="3">
         <f>(F19*1000)/B19</f>
         <v>39916.199999999997</v>
       </c>
-      <c r="H19" s="6" t="s">
+      <c r="H19" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I19" s="7"/>
-      <c r="K19" s="5" t="s">
+      <c r="I19" s="4"/>
+      <c r="K19" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="L19" s="6">
+      <c r="L19" s="3">
         <v>500</v>
       </c>
-      <c r="M19" s="6">
+      <c r="M19" s="3">
         <f>O19/P19/1000</f>
         <v>7.7161653664426977E-5</v>
       </c>
-      <c r="N19" s="6">
+      <c r="N19" s="3">
         <f t="shared" si="4"/>
         <v>3.8580826832213491E-2</v>
       </c>
-      <c r="O19" s="6">
+      <c r="O19" s="3">
         <v>1540</v>
       </c>
-      <c r="P19" s="6">
+      <c r="P19" s="3">
         <v>19958.099999999999</v>
       </c>
-      <c r="Q19" s="6">
+      <c r="Q19" s="3">
         <f>(P19*1000)/L19</f>
         <v>39916.199999999997</v>
       </c>
-      <c r="R19" s="6" t="s">
+      <c r="R19" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="S19" s="7"/>
-      <c r="U19" s="5" t="s">
+      <c r="S19" s="4"/>
+      <c r="U19" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="V19" s="6">
+      <c r="V19" s="3">
         <v>500</v>
       </c>
-      <c r="W19" s="6">
+      <c r="W19" s="3">
         <f>Y19/Z19/1000</f>
         <v>7.7161653664426977E-5</v>
       </c>
-      <c r="X19" s="6">
+      <c r="X19" s="3">
         <f>V19*W19</f>
         <v>3.8580826832213491E-2</v>
       </c>
-      <c r="Y19" s="6">
+      <c r="Y19" s="3">
         <v>1540</v>
       </c>
-      <c r="Z19" s="6">
+      <c r="Z19" s="3">
         <v>19958.099999999999</v>
       </c>
-      <c r="AA19" s="6">
+      <c r="AA19" s="3">
         <f>(Z19*1000)/V19</f>
         <v>39916.199999999997</v>
       </c>
-      <c r="AB19" s="6" t="s">
+      <c r="AB19" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="AC19" s="7"/>
+      <c r="AC19" s="4"/>
     </row>
     <row r="20" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B20" s="6">
+      <c r="B20" s="3">
         <v>6000</v>
       </c>
-      <c r="C20" s="6">
+      <c r="C20" s="3">
         <f>E20/F20/1000</f>
         <v>2.1200400000000001E-5</v>
       </c>
-      <c r="D20" s="6">
+      <c r="D20" s="3">
         <f t="shared" si="3"/>
         <v>0.12720239999999999</v>
       </c>
-      <c r="E20" s="6">
+      <c r="E20" s="3">
         <v>530.01</v>
       </c>
-      <c r="F20" s="6">
+      <c r="F20" s="3">
         <v>25000</v>
       </c>
-      <c r="G20" s="6">
+      <c r="G20" s="3">
         <f>(F20*1000)/B20</f>
         <v>4166.666666666667</v>
       </c>
-      <c r="H20" s="6" t="s">
+      <c r="H20" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="I20" s="7"/>
-      <c r="K20" s="5" t="s">
+      <c r="I20" s="4"/>
+      <c r="K20" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="L20" s="6">
+      <c r="L20" s="3">
         <v>6000</v>
       </c>
-      <c r="M20" s="6">
+      <c r="M20" s="3">
         <f>O20/P20/1000</f>
         <v>2.1200400000000001E-5</v>
       </c>
-      <c r="N20" s="6">
+      <c r="N20" s="3">
         <f t="shared" si="4"/>
         <v>0.12720239999999999</v>
       </c>
-      <c r="O20" s="6">
+      <c r="O20" s="3">
         <v>530.01</v>
       </c>
-      <c r="P20" s="6">
+      <c r="P20" s="3">
         <v>25000</v>
       </c>
-      <c r="Q20" s="6">
+      <c r="Q20" s="3">
         <f>(P20*1000)/L20</f>
         <v>4166.666666666667</v>
       </c>
-      <c r="R20" s="6" t="s">
+      <c r="R20" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="S20" s="7"/>
-      <c r="U20" s="5" t="s">
+      <c r="S20" s="4"/>
+      <c r="U20" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="V20" s="6">
+      <c r="V20" s="3">
         <v>6000</v>
       </c>
-      <c r="W20" s="6">
+      <c r="W20" s="3">
         <f>Y20/Z20/1000</f>
         <v>2.1200400000000001E-5</v>
       </c>
-      <c r="X20" s="6">
+      <c r="X20" s="3">
         <f>V20*W20</f>
         <v>0.12720239999999999</v>
       </c>
-      <c r="Y20" s="6">
+      <c r="Y20" s="3">
         <v>530.01</v>
       </c>
-      <c r="Z20" s="6">
+      <c r="Z20" s="3">
         <v>25000</v>
       </c>
-      <c r="AA20" s="6">
+      <c r="AA20" s="3">
         <f>(Z20*1000)/V20</f>
         <v>4166.666666666667</v>
       </c>
-      <c r="AB20" s="6" t="s">
+      <c r="AB20" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AC20" s="7"/>
+      <c r="AC20" s="4"/>
     </row>
     <row r="21" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B21" s="6">
+      <c r="B21" s="3">
         <v>1800</v>
       </c>
-      <c r="C21" s="6">
+      <c r="C21" s="3">
         <f>E21/F21/1000</f>
         <v>1.34324E-5</v>
       </c>
-      <c r="D21" s="6">
+      <c r="D21" s="3">
         <f t="shared" si="3"/>
         <v>2.417832E-2</v>
       </c>
-      <c r="E21" s="6">
+      <c r="E21" s="3">
         <v>335.81</v>
       </c>
-      <c r="F21" s="6">
+      <c r="F21" s="3">
         <v>25000</v>
       </c>
-      <c r="G21" s="6">
+      <c r="G21" s="3">
         <f>(F21*1000)/B21</f>
         <v>13888.888888888889</v>
       </c>
-      <c r="H21" s="6" t="s">
+      <c r="H21" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="I21" s="7"/>
-      <c r="K21" s="5" t="s">
+      <c r="I21" s="4"/>
+      <c r="K21" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="L21" s="6">
+      <c r="L21" s="3">
         <v>1800</v>
       </c>
-      <c r="M21" s="6">
+      <c r="M21" s="3">
         <f>O21/P21/1000</f>
         <v>1.34324E-5</v>
       </c>
-      <c r="N21" s="6">
+      <c r="N21" s="3">
         <f t="shared" si="4"/>
         <v>2.417832E-2</v>
       </c>
-      <c r="O21" s="6">
+      <c r="O21" s="3">
         <v>335.81</v>
       </c>
-      <c r="P21" s="6">
+      <c r="P21" s="3">
         <v>25000</v>
       </c>
-      <c r="Q21" s="6">
+      <c r="Q21" s="3">
         <f>(P21*1000)/L21</f>
         <v>13888.888888888889</v>
       </c>
-      <c r="R21" s="6" t="s">
+      <c r="R21" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="S21" s="7"/>
-      <c r="U21" s="5" t="s">
+      <c r="S21" s="4"/>
+      <c r="U21" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="V21" s="6">
+      <c r="V21" s="3">
         <v>1800</v>
       </c>
-      <c r="W21" s="6">
+      <c r="W21" s="3">
         <f>Y21/Z21/1000</f>
         <v>1.34324E-5</v>
       </c>
-      <c r="X21" s="6">
+      <c r="X21" s="3">
         <f>V21*W21</f>
         <v>2.417832E-2</v>
       </c>
-      <c r="Y21" s="6">
+      <c r="Y21" s="3">
         <v>335.81</v>
       </c>
-      <c r="Z21" s="6">
+      <c r="Z21" s="3">
         <v>25000</v>
       </c>
-      <c r="AA21" s="6">
+      <c r="AA21" s="3">
         <f>(Z21*1000)/V21</f>
         <v>13888.888888888889</v>
       </c>
-      <c r="AB21" s="6" t="s">
+      <c r="AB21" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="AC21" s="7"/>
+      <c r="AC21" s="4"/>
     </row>
     <row r="22" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="6"/>
-      <c r="C22" s="6"/>
-      <c r="D22" s="6">
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+      <c r="D22" s="3">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="7"/>
-      <c r="K22" s="5" t="s">
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="4"/>
+      <c r="K22" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="L22" s="6"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="6">
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+      <c r="N22" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O22" s="6"/>
-      <c r="P22" s="6"/>
-      <c r="Q22" s="6"/>
-      <c r="R22" s="6"/>
-      <c r="S22" s="7"/>
-      <c r="U22" s="5" t="s">
+      <c r="O22" s="3"/>
+      <c r="P22" s="3"/>
+      <c r="Q22" s="3"/>
+      <c r="R22" s="3"/>
+      <c r="S22" s="4"/>
+      <c r="U22" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="V22" s="6"/>
-      <c r="W22" s="6"/>
-      <c r="X22" s="6"/>
-      <c r="Y22" s="6"/>
-      <c r="Z22" s="6"/>
-      <c r="AA22" s="6"/>
-      <c r="AB22" s="6"/>
-      <c r="AC22" s="7"/>
+      <c r="V22" s="3"/>
+      <c r="W22" s="3"/>
+      <c r="X22" s="3"/>
+      <c r="Y22" s="3"/>
+      <c r="Z22" s="3"/>
+      <c r="AA22" s="3"/>
+      <c r="AB22" s="3"/>
+      <c r="AC22" s="4"/>
     </row>
     <row r="23" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6">
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="I23" s="7"/>
-      <c r="K23" s="5" t="s">
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="I23" s="4"/>
+      <c r="K23" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="L23" s="6"/>
-      <c r="M23" s="6"/>
-      <c r="N23" s="6">
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O23" s="6"/>
-      <c r="P23" s="6"/>
-      <c r="S23" s="7"/>
-      <c r="U23" s="5" t="s">
+      <c r="O23" s="3"/>
+      <c r="P23" s="3"/>
+      <c r="S23" s="4"/>
+      <c r="U23" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="V23" s="6"/>
-      <c r="W23" s="6"/>
-      <c r="X23" s="6"/>
-      <c r="Y23" s="6"/>
-      <c r="Z23" s="6"/>
-      <c r="AC23" s="7"/>
+      <c r="V23" s="3"/>
+      <c r="W23" s="3"/>
+      <c r="X23" s="3"/>
+      <c r="Y23" s="3"/>
+      <c r="Z23" s="3"/>
+      <c r="AC23" s="4"/>
     </row>
     <row r="24" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B24" s="6"/>
-      <c r="C24" s="6"/>
-      <c r="D24" s="6">
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+      <c r="D24" s="3">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="I24" s="7"/>
-      <c r="K24" s="5" t="s">
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="I24" s="4"/>
+      <c r="K24" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="L24" s="6"/>
-      <c r="M24" s="6"/>
-      <c r="N24" s="6">
+      <c r="L24" s="3"/>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O24" s="6"/>
-      <c r="P24" s="6"/>
-      <c r="Q24" s="6"/>
-      <c r="R24" s="6"/>
-      <c r="S24" s="7"/>
-      <c r="U24" s="5" t="s">
+      <c r="O24" s="3"/>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="3"/>
+      <c r="S24" s="4"/>
+      <c r="U24" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="V24" s="6"/>
-      <c r="W24" s="6"/>
-      <c r="X24" s="6"/>
-      <c r="Y24" s="6"/>
-      <c r="Z24" s="6"/>
-      <c r="AC24" s="7"/>
+      <c r="V24" s="3"/>
+      <c r="W24" s="3"/>
+      <c r="X24" s="3"/>
+      <c r="Y24" s="3"/>
+      <c r="Z24" s="3"/>
+      <c r="AC24" s="4"/>
     </row>
     <row r="25" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B25" s="14">
+      <c r="B25" s="11">
         <v>0.4</v>
       </c>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6">
+      <c r="C25" s="3"/>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3">
         <f>MIN(G17:G21)</f>
         <v>4166.666666666667</v>
       </c>
-      <c r="H25" s="6" t="s">
+      <c r="H25" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I25" s="7"/>
-      <c r="K25" s="5" t="s">
+      <c r="I25" s="4"/>
+      <c r="K25" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="L25" s="14">
+      <c r="L25" s="11">
         <v>0.4</v>
       </c>
-      <c r="M25" s="6"/>
-      <c r="N25" s="6"/>
-      <c r="O25" s="6"/>
-      <c r="P25" s="6"/>
-      <c r="Q25" s="6">
+      <c r="M25" s="3"/>
+      <c r="N25" s="3"/>
+      <c r="O25" s="3"/>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="3">
         <f>MIN(Q17:Q21)</f>
         <v>4166.666666666667</v>
       </c>
-      <c r="R25" s="6" t="s">
+      <c r="R25" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="S25" s="7"/>
-      <c r="U25" s="5" t="s">
+      <c r="S25" s="4"/>
+      <c r="U25" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="V25" s="14">
+      <c r="V25" s="11">
         <v>0.4</v>
       </c>
-      <c r="W25" s="6"/>
-      <c r="X25" s="6"/>
-      <c r="Y25" s="6"/>
-      <c r="Z25" s="6"/>
-      <c r="AA25" s="6">
+      <c r="W25" s="3"/>
+      <c r="X25" s="3"/>
+      <c r="Y25" s="3"/>
+      <c r="Z25" s="3"/>
+      <c r="AA25" s="3">
         <f>MIN(AA17:AA21)</f>
         <v>4166.666666666667</v>
       </c>
-      <c r="AB25" s="6" t="s">
+      <c r="AB25" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="AC25" s="7"/>
+      <c r="AC25" s="4"/>
     </row>
     <row r="26" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B26" s="9">
+      <c r="B26" s="6">
         <f>SUM(B17:B21)/1000</f>
         <v>13.55</v>
       </c>
-      <c r="C26" s="9">
+      <c r="C26" s="6">
         <f>SUM(C17:C21)</f>
         <v>1.7063965366442697E-4</v>
       </c>
-      <c r="D26" s="9">
+      <c r="D26" s="6">
         <f>SUM(D17:D24)</f>
         <v>0.27185874683221345</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="E26" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F26" s="10"/>
-      <c r="G26" s="6">
+      <c r="F26" s="7"/>
+      <c r="G26" s="3">
         <f>G25/B27</f>
         <v>416.66666666666669</v>
       </c>
-      <c r="H26" s="6" t="s">
+      <c r="H26" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="I26" s="7"/>
-      <c r="K26" s="8" t="s">
+      <c r="I26" s="4"/>
+      <c r="K26" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L26" s="9">
+      <c r="L26" s="6">
         <f>SUM(L17:L21)/1000</f>
         <v>8.5500000000000007</v>
       </c>
-      <c r="M26" s="9">
+      <c r="M26" s="6">
         <f>SUM(M17:M21)</f>
         <v>1.5649525366442696E-4</v>
       </c>
-      <c r="N26" s="9">
+      <c r="N26" s="6">
         <f>SUM(N17:N24)</f>
         <v>0.20113674683221347</v>
       </c>
-      <c r="O26" s="6" t="s">
+      <c r="O26" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="P26" s="10"/>
-      <c r="Q26" s="6">
+      <c r="P26" s="7"/>
+      <c r="Q26" s="3">
         <f>Q25/L27</f>
         <v>416.66666666666669</v>
       </c>
-      <c r="R26" s="6" t="s">
+      <c r="R26" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="S26" s="7"/>
-      <c r="U26" s="8" t="s">
+      <c r="S26" s="4"/>
+      <c r="U26" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="V26" s="9">
+      <c r="V26" s="6">
         <f>SUM(V17:V21)/1000</f>
         <v>8.3000000000000007</v>
       </c>
-      <c r="W26" s="9">
+      <c r="W26" s="6">
         <f>SUM(W17:W21)</f>
         <v>1.1179445366442698E-4</v>
       </c>
-      <c r="X26" s="6">
+      <c r="X26" s="3">
         <f>SUM(X17:X24)</f>
         <v>0.18996154683221347</v>
       </c>
-      <c r="Y26" s="6" t="s">
+      <c r="Y26" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="Z26" s="10">
+      <c r="Z26" s="7">
         <f>V26*W26</f>
         <v>9.2789396541474408E-4</v>
       </c>
-      <c r="AA26" s="6">
+      <c r="AA26" s="3">
         <f>AA25/V27</f>
         <v>416.66666666666669</v>
       </c>
-      <c r="AB26" s="6" t="s">
+      <c r="AB26" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="AC26" s="7"/>
+      <c r="AC26" s="4"/>
     </row>
     <row r="27" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A27" s="11" t="s">
+      <c r="A27" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="B27" s="12">
+      <c r="B27" s="9">
         <v>10</v>
       </c>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12">
+      <c r="C27" s="9"/>
+      <c r="D27" s="9">
         <f>D26*B27</f>
         <v>2.7185874683221343</v>
       </c>
-      <c r="E27" s="12" t="s">
+      <c r="E27" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="F27" s="12"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="13"/>
-      <c r="K27" s="11" t="s">
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="10"/>
+      <c r="K27" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="L27" s="12">
+      <c r="L27" s="9">
         <v>10</v>
       </c>
-      <c r="M27" s="12"/>
-      <c r="N27" s="12">
+      <c r="M27" s="9"/>
+      <c r="N27" s="9">
         <f>N26*L27</f>
         <v>2.0113674683221348</v>
       </c>
-      <c r="O27" s="12" t="s">
+      <c r="O27" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="P27" s="12"/>
-      <c r="Q27" s="12"/>
-      <c r="R27" s="12"/>
-      <c r="S27" s="13"/>
-      <c r="U27" s="11" t="s">
+      <c r="P27" s="9"/>
+      <c r="Q27" s="9"/>
+      <c r="R27" s="9"/>
+      <c r="S27" s="10"/>
+      <c r="U27" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="V27" s="12">
+      <c r="V27" s="9">
         <v>10</v>
       </c>
-      <c r="W27" s="12"/>
-      <c r="X27" s="12">
+      <c r="W27" s="9"/>
+      <c r="X27" s="9">
         <f>X26*V27</f>
         <v>1.8996154683221347</v>
       </c>
-      <c r="Y27" s="12" t="s">
+      <c r="Y27" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="Z27" s="12">
+      <c r="Z27" s="9">
         <f>V27*Z26</f>
         <v>9.278939654147441E-3</v>
       </c>
-      <c r="AA27" s="12"/>
-      <c r="AB27" s="12"/>
-      <c r="AC27" s="13"/>
+      <c r="AA27" s="9"/>
+      <c r="AB27" s="9"/>
+      <c r="AC27" s="10"/>
     </row>
     <row r="28" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A28" s="16" t="s">
+      <c r="A28" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="B28" s="6">
+      <c r="B28" s="3">
         <v>12.5</v>
       </c>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6" t="s">
+      <c r="C28" s="3"/>
+      <c r="D28" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E28" s="6">
+      <c r="E28" s="3">
         <f>SUM(E17:E24)</f>
         <v>3876.9500000000003</v>
       </c>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6"/>
-      <c r="K28" s="16" t="s">
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="K28" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="L28" s="6">
+      <c r="L28" s="3">
         <v>10</v>
       </c>
-      <c r="M28" s="6"/>
-      <c r="N28" s="6" t="s">
+      <c r="M28" s="3"/>
+      <c r="N28" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="O28" s="6">
+      <c r="O28" s="3">
         <f>SUM(O17:O24)</f>
         <v>3523.3399999999997</v>
       </c>
-      <c r="P28" s="6"/>
-      <c r="Q28" s="6"/>
-      <c r="R28" s="6"/>
-      <c r="S28" s="6"/>
-      <c r="U28" s="16" t="s">
+      <c r="P28" s="3"/>
+      <c r="Q28" s="3"/>
+      <c r="R28" s="3"/>
+      <c r="S28" s="3"/>
+      <c r="U28" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="V28" s="6">
+      <c r="V28" s="3">
         <v>10</v>
       </c>
-      <c r="W28" s="6"/>
-      <c r="X28" s="6" t="s">
+      <c r="W28" s="3"/>
+      <c r="X28" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="Y28" s="6">
+      <c r="Y28" s="3">
         <f>SUM(Y17:Y24)</f>
         <v>2405.8200000000002</v>
       </c>
-      <c r="Z28" s="6"/>
-      <c r="AA28" s="6"/>
-      <c r="AB28" s="6"/>
-      <c r="AC28" s="6"/>
+      <c r="Z28" s="3"/>
+      <c r="AA28" s="3"/>
+      <c r="AB28" s="3"/>
+      <c r="AC28" s="3"/>
     </row>
     <row r="29" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="E29" s="4">
+      <c r="E29" s="1">
         <f>B28*G26</f>
         <v>5208.3333333333339</v>
       </c>
-      <c r="N29" s="4" t="s">
+      <c r="N29" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="O29" s="4">
+      <c r="O29" s="1">
         <f>L28*Q26</f>
         <v>4166.666666666667</v>
       </c>
-      <c r="X29" s="4" t="s">
+      <c r="X29" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="Y29" s="4">
+      <c r="Y29" s="1">
         <f>V28*AA26</f>
         <v>4166.666666666667</v>
       </c>
     </row>
     <row r="30" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="E30" s="4">
+      <c r="E30" s="1">
         <f>E29-E28</f>
         <v>1331.3833333333337</v>
       </c>
-      <c r="N30" s="4" t="s">
+      <c r="N30" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="O30" s="4">
+      <c r="O30" s="1">
         <f>O29-O28</f>
         <v>643.32666666666728</v>
       </c>
-      <c r="X30" s="4" t="s">
+      <c r="X30" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="Y30" s="4">
+      <c r="Y30" s="1">
         <f>Y29-Y28</f>
         <v>1760.8466666666668</v>
       </c>
     </row>
     <row r="31" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E31" s="4">
+      <c r="E31" s="1">
         <f>1 - E28/E29</f>
         <v>0.25562560000000001</v>
       </c>
-      <c r="N31" s="4" t="s">
+      <c r="N31" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="O31" s="4">
+      <c r="O31" s="1">
         <f>1 - O28/O29</f>
         <v>0.15439840000000016</v>
       </c>
-      <c r="X31" s="4" t="s">
+      <c r="X31" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="Y31" s="4">
+      <c r="Y31" s="1">
         <f>1 - Y28/Y29</f>
         <v>0.42260319999999996</v>
       </c>
